--- a/public/exports-from-60/29189889.xlsx
+++ b/public/exports-from-60/29189889.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">200050263</t>
+          <t xml:space="preserve">200050268</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -11389,12 +11389,12 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311053859</t>
+          <t xml:space="preserve">311053869</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">factum2 Horsens</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311084316</t>
+          <t xml:space="preserve">311084392</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">

--- a/public/exports-from-60/29189889.xlsx
+++ b/public/exports-from-60/29189889.xlsx
@@ -9664,7 +9664,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">200050268</t>
+          <t xml:space="preserve">200050263</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -16279,12 +16279,12 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -16354,12 +16354,12 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>

--- a/public/exports-from-60/29189889.xlsx
+++ b/public/exports-from-60/29189889.xlsx
@@ -11389,12 +11389,12 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311053869</t>
+          <t xml:space="preserve">311053859</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">factum2 Horsens</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311084392</t>
+          <t xml:space="preserve">311084316</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -16429,12 +16429,12 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -16504,12 +16504,12 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -16579,12 +16579,12 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -16654,12 +16654,12 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -16729,12 +16729,12 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -16804,12 +16804,12 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -16879,12 +16879,12 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
